--- a/Result/profitability/6177.xlsx
+++ b/Result/profitability/6177.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.43125</v>
+        <v>1.615</v>
       </c>
       <c r="N2" t="n">
-        <v>27.7425</v>
+        <v>28.89</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.74</v>
       </c>
       <c r="M3" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="N3" t="n">
-        <v>26.7525</v>
+        <v>25.9975</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>1.235</v>
+        <v>1.44125</v>
       </c>
       <c r="N4" t="n">
-        <v>24.2475</v>
+        <v>25.99125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14125</v>
+        <v>1.34125</v>
       </c>
       <c r="N5" t="n">
-        <v>5.407499999999999</v>
+        <v>6.427499999999998</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>-0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11375</v>
+        <v>1.29875</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1246,7 +1246,7 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>0.76</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1361,7 +1361,7 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5525</v>
+        <v>0.29875</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9776,6 +9776,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3466</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2327</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1139</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>874</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>25.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>884</v>
+      </c>
+      <c r="K75" t="n">
+        <v>709</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.62875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.5025</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5750708215297451</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-17.19</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3433879344786257</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.159999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3302306758397409</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
